--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,1922 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>133792029</v>
+      </c>
+      <c r="B3" t="n">
+        <v>79412</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>864</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Knottrig blåslav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Hypogymnia bitteri</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>471436</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6868747</v>
+      </c>
+      <c r="S3" t="n">
+        <v>20</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>133793871</v>
+      </c>
+      <c r="B4" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>471563</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6868622</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>133793537</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>471525</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6868589</v>
+      </c>
+      <c r="S5" t="n">
+        <v>20</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>133789913</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>471488</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6869113</v>
+      </c>
+      <c r="S6" t="n">
+        <v>20</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>133793581</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>471520</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6868576</v>
+      </c>
+      <c r="S7" t="n">
+        <v>20</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>133790434</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57145</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>471540</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6869075</v>
+      </c>
+      <c r="S8" t="n">
+        <v>20</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Noterat färsk spillning.</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>133793754</v>
+      </c>
+      <c r="B9" t="n">
+        <v>80438</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>471567</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6868568</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>133794062</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>471554</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6868632</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>133793032</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>471433</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6868656</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fem meter söder om stormfälld tall.</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>133794314</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>471536</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6868645</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>133791426</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>185</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>471421</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6868947</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133794178</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>471548</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6868633</v>
+      </c>
+      <c r="S14" t="n">
+        <v>20</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>133792769</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>471449</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6868656</v>
+      </c>
+      <c r="S15" t="n">
+        <v>20</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>133791850</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79923</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>471361</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6868809</v>
+      </c>
+      <c r="S16" t="n">
+        <v>20</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>133791766</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79090</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>471393</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6868865</v>
+      </c>
+      <c r="S17" t="n">
+        <v>20</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>133790857</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79365</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>185</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Violettgrå tagellav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Bryoria nadvornikiana</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>471491</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6869006</v>
+      </c>
+      <c r="S18" t="n">
+        <v>20</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>133791855</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78340</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6487</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blågrå svartspik</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis fennica</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>471361</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6868809</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>133794480</v>
+      </c>
+      <c r="B20" t="n">
+        <v>99130</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>471529</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6868615</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>133794598</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79091</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>471520</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6868626</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Sveg</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>lennart karlsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -1580,7 +1580,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133793032</v>
+        <v>133794314</v>
       </c>
       <c r="B11" t="n">
         <v>99130</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471433</v>
+        <v>471536</v>
       </c>
       <c r="R11" t="n">
-        <v>6868656</v>
+        <v>6868645</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,11 +1660,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1691,7 +1686,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133794314</v>
+        <v>133793032</v>
       </c>
       <c r="B12" t="n">
         <v>99130</v>
@@ -1721,7 +1716,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1735,13 +1730,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471536</v>
+        <v>471433</v>
       </c>
       <c r="R12" t="n">
-        <v>6868645</v>
+        <v>6868656</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,6 +1766,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2300,45 +2300,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133790857</v>
+        <v>133794480</v>
       </c>
       <c r="B18" t="n">
-        <v>79365</v>
+        <v>99130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471491</v>
+        <v>471529</v>
       </c>
       <c r="R18" t="n">
-        <v>6869006</v>
+        <v>6868615</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2397,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133791855</v>
+        <v>133790857</v>
       </c>
       <c r="B19" t="n">
-        <v>78340</v>
+        <v>79365</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2432,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471361</v>
+        <v>471491</v>
       </c>
       <c r="R19" t="n">
-        <v>6868809</v>
+        <v>6869006</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2494,54 +2503,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133794480</v>
+        <v>133791855</v>
       </c>
       <c r="B20" t="n">
-        <v>99130</v>
+        <v>78340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471529</v>
+        <v>471361</v>
       </c>
       <c r="R20" t="n">
-        <v>6868615</v>
+        <v>6868809</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133792029</v>
       </c>
       <c r="B3" t="n">
-        <v>79412</v>
+        <v>79413</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>133793871</v>
       </c>
       <c r="B4" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>133793537</v>
       </c>
       <c r="B5" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>133789913</v>
       </c>
       <c r="B6" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>133793581</v>
       </c>
       <c r="B7" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133793754</v>
+        <v>133794062</v>
       </c>
       <c r="B9" t="n">
-        <v>80438</v>
+        <v>79092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471567</v>
+        <v>471554</v>
       </c>
       <c r="R9" t="n">
-        <v>6868568</v>
+        <v>6868632</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133794062</v>
+        <v>133793754</v>
       </c>
       <c r="B10" t="n">
-        <v>79091</v>
+        <v>80439</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471554</v>
+        <v>471567</v>
       </c>
       <c r="R10" t="n">
-        <v>6868632</v>
+        <v>6868568</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133794314</v>
+        <v>133793032</v>
       </c>
       <c r="B11" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471536</v>
+        <v>471433</v>
       </c>
       <c r="R11" t="n">
-        <v>6868645</v>
+        <v>6868656</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,6 +1660,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133793032</v>
+        <v>133794314</v>
       </c>
       <c r="B12" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,7 +1721,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1730,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471433</v>
+        <v>471536</v>
       </c>
       <c r="R12" t="n">
-        <v>6868656</v>
+        <v>6868645</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,7 +1800,7 @@
         <v>133791426</v>
       </c>
       <c r="B13" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133794178</v>
       </c>
       <c r="B14" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>133792769</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2109,7 +2109,7 @@
         <v>133791850</v>
       </c>
       <c r="B16" t="n">
-        <v>79923</v>
+        <v>79924</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>133791766</v>
       </c>
       <c r="B17" t="n">
-        <v>79090</v>
+        <v>79091</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>133794480</v>
       </c>
       <c r="B18" t="n">
-        <v>99130</v>
+        <v>99132</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>133790857</v>
       </c>
       <c r="B19" t="n">
-        <v>79365</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2506,7 +2506,7 @@
         <v>133791855</v>
       </c>
       <c r="B20" t="n">
-        <v>78340</v>
+        <v>78341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>133794598</v>
       </c>
       <c r="B21" t="n">
-        <v>79091</v>
+        <v>79092</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -2300,54 +2300,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133794480</v>
+        <v>133791855</v>
       </c>
       <c r="B18" t="n">
-        <v>99132</v>
+        <v>78341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471529</v>
+        <v>471361</v>
       </c>
       <c r="R18" t="n">
-        <v>6868615</v>
+        <v>6868809</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2503,45 +2494,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133791855</v>
+        <v>133794480</v>
       </c>
       <c r="B20" t="n">
-        <v>78341</v>
+        <v>99132</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471361</v>
+        <v>471529</v>
       </c>
       <c r="R20" t="n">
-        <v>6868809</v>
+        <v>6868615</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>133793537</v>
       </c>
       <c r="B5" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>133793581</v>
       </c>
       <c r="B7" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133794062</v>
+        <v>133793754</v>
       </c>
       <c r="B9" t="n">
-        <v>79092</v>
+        <v>80439</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471554</v>
+        <v>471567</v>
       </c>
       <c r="R9" t="n">
-        <v>6868632</v>
+        <v>6868568</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133793754</v>
+        <v>133794062</v>
       </c>
       <c r="B10" t="n">
-        <v>80439</v>
+        <v>79092</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471567</v>
+        <v>471554</v>
       </c>
       <c r="R10" t="n">
-        <v>6868568</v>
+        <v>6868632</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1583,7 +1583,7 @@
         <v>133793032</v>
       </c>
       <c r="B11" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>133794314</v>
       </c>
       <c r="B12" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133794178</v>
       </c>
       <c r="B14" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>133792769</v>
       </c>
       <c r="B15" t="n">
-        <v>99132</v>
+        <v>99138</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2300,45 +2300,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133791855</v>
+        <v>133794480</v>
       </c>
       <c r="B18" t="n">
-        <v>78341</v>
+        <v>99138</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471361</v>
+        <v>471529</v>
       </c>
       <c r="R18" t="n">
-        <v>6868809</v>
+        <v>6868615</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2494,54 +2503,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133794480</v>
+        <v>133791855</v>
       </c>
       <c r="B20" t="n">
-        <v>99132</v>
+        <v>78341</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471529</v>
+        <v>471361</v>
       </c>
       <c r="R20" t="n">
-        <v>6868615</v>
+        <v>6868809</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -978,7 +978,7 @@
         <v>133793537</v>
       </c>
       <c r="B5" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>133793581</v>
       </c>
       <c r="B7" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>133793032</v>
       </c>
       <c r="B11" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>133794314</v>
       </c>
       <c r="B12" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133794178</v>
       </c>
       <c r="B14" t="n">
-        <v>99138</v>
+        <v>99140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2000,54 +2000,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133792769</v>
+        <v>133791850</v>
       </c>
       <c r="B15" t="n">
-        <v>99138</v>
+        <v>79924</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471449</v>
+        <v>471361</v>
       </c>
       <c r="R15" t="n">
-        <v>6868656</v>
+        <v>6868809</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2106,45 +2097,54 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133791850</v>
+        <v>133792769</v>
       </c>
       <c r="B16" t="n">
-        <v>79924</v>
+        <v>99140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471361</v>
+        <v>471449</v>
       </c>
       <c r="R16" t="n">
-        <v>6868809</v>
+        <v>6868656</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2300,54 +2300,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133794480</v>
+        <v>133791855</v>
       </c>
       <c r="B18" t="n">
-        <v>99138</v>
+        <v>78341</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471529</v>
+        <v>471361</v>
       </c>
       <c r="R18" t="n">
-        <v>6868615</v>
+        <v>6868809</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2503,45 +2494,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133791855</v>
+        <v>133794480</v>
       </c>
       <c r="B20" t="n">
-        <v>78341</v>
+        <v>99140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471361</v>
+        <v>471529</v>
       </c>
       <c r="R20" t="n">
-        <v>6868809</v>
+        <v>6868615</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -2300,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133791855</v>
+        <v>133790857</v>
       </c>
       <c r="B18" t="n">
-        <v>78341</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471361</v>
+        <v>471491</v>
       </c>
       <c r="R18" t="n">
-        <v>6868809</v>
+        <v>6869006</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133790857</v>
+        <v>133791855</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>78341</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471491</v>
+        <v>471361</v>
       </c>
       <c r="R19" t="n">
-        <v>6869006</v>
+        <v>6868809</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -2300,45 +2300,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133790857</v>
+        <v>133794480</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>99140</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471491</v>
+        <v>471529</v>
       </c>
       <c r="R18" t="n">
-        <v>6869006</v>
+        <v>6868615</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2494,54 +2503,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133794480</v>
+        <v>133790857</v>
       </c>
       <c r="B20" t="n">
-        <v>99140</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471529</v>
+        <v>471491</v>
       </c>
       <c r="R20" t="n">
-        <v>6868615</v>
+        <v>6869006</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -2300,54 +2300,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133794480</v>
+        <v>133790857</v>
       </c>
       <c r="B18" t="n">
-        <v>99140</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471529</v>
+        <v>471491</v>
       </c>
       <c r="R18" t="n">
-        <v>6868615</v>
+        <v>6869006</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2503,45 +2494,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133790857</v>
+        <v>133794480</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>99140</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471491</v>
+        <v>471529</v>
       </c>
       <c r="R20" t="n">
-        <v>6869006</v>
+        <v>6868615</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133792029</v>
       </c>
       <c r="B3" t="n">
-        <v>79413</v>
+        <v>79427</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>133793871</v>
       </c>
       <c r="B4" t="n">
-        <v>79092</v>
+        <v>79106</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>133793537</v>
       </c>
       <c r="B5" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>133789913</v>
       </c>
       <c r="B6" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>133793581</v>
       </c>
       <c r="B7" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>133790434</v>
       </c>
       <c r="B8" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1386,10 +1386,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133793754</v>
+        <v>133794062</v>
       </c>
       <c r="B9" t="n">
-        <v>80439</v>
+        <v>79106</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1397,21 +1397,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471567</v>
+        <v>471554</v>
       </c>
       <c r="R9" t="n">
-        <v>6868568</v>
+        <v>6868632</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1483,10 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133794062</v>
+        <v>133793754</v>
       </c>
       <c r="B10" t="n">
-        <v>79092</v>
+        <v>80453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1494,21 +1494,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471554</v>
+        <v>471567</v>
       </c>
       <c r="R10" t="n">
-        <v>6868632</v>
+        <v>6868568</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1583,7 +1583,7 @@
         <v>133793032</v>
       </c>
       <c r="B11" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>133794314</v>
       </c>
       <c r="B12" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>133791426</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>79380</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133794178</v>
       </c>
       <c r="B14" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>133791850</v>
       </c>
       <c r="B15" t="n">
-        <v>79924</v>
+        <v>79938</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>133792769</v>
       </c>
       <c r="B16" t="n">
-        <v>99140</v>
+        <v>99168</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>133791766</v>
       </c>
       <c r="B17" t="n">
-        <v>79091</v>
+        <v>79105</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,54 +2300,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133794480</v>
+        <v>133790857</v>
       </c>
       <c r="B18" t="n">
-        <v>99140</v>
+        <v>79380</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471529</v>
+        <v>471491</v>
       </c>
       <c r="R18" t="n">
-        <v>6868615</v>
+        <v>6869006</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2409,7 +2400,7 @@
         <v>133791855</v>
       </c>
       <c r="B19" t="n">
-        <v>78341</v>
+        <v>78352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2503,45 +2494,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133790857</v>
+        <v>133794480</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>99168</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471491</v>
+        <v>471529</v>
       </c>
       <c r="R20" t="n">
-        <v>6869006</v>
+        <v>6868615</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2603,7 +2603,7 @@
         <v>133794598</v>
       </c>
       <c r="B21" t="n">
-        <v>79092</v>
+        <v>79106</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133792029</v>
       </c>
       <c r="B3" t="n">
-        <v>79427</v>
+        <v>79437</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>133793871</v>
       </c>
       <c r="B4" t="n">
-        <v>79106</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>133793537</v>
       </c>
       <c r="B5" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>133789913</v>
       </c>
       <c r="B6" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>133793581</v>
       </c>
       <c r="B7" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1287,7 +1287,7 @@
         <v>133790434</v>
       </c>
       <c r="B8" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>133794062</v>
       </c>
       <c r="B9" t="n">
-        <v>79106</v>
+        <v>79116</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>133793754</v>
       </c>
       <c r="B10" t="n">
-        <v>80453</v>
+        <v>80473</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>133793032</v>
       </c>
       <c r="B11" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>133794314</v>
       </c>
       <c r="B12" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>133791426</v>
       </c>
       <c r="B13" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133794178</v>
       </c>
       <c r="B14" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>133791850</v>
       </c>
       <c r="B15" t="n">
-        <v>79938</v>
+        <v>79948</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>133792769</v>
       </c>
       <c r="B16" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>133791766</v>
       </c>
       <c r="B17" t="n">
-        <v>79105</v>
+        <v>79115</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>133790857</v>
       </c>
       <c r="B18" t="n">
-        <v>79380</v>
+        <v>79390</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2400,7 +2400,7 @@
         <v>133791855</v>
       </c>
       <c r="B19" t="n">
-        <v>78352</v>
+        <v>78362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>133794480</v>
       </c>
       <c r="B20" t="n">
-        <v>99168</v>
+        <v>99178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2603,7 +2603,7 @@
         <v>133794598</v>
       </c>
       <c r="B21" t="n">
-        <v>79106</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -2300,45 +2300,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133790857</v>
+        <v>133794480</v>
       </c>
       <c r="B18" t="n">
-        <v>79390</v>
+        <v>99178</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471491</v>
+        <v>471529</v>
       </c>
       <c r="R18" t="n">
-        <v>6869006</v>
+        <v>6868615</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2397,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133791855</v>
+        <v>133790857</v>
       </c>
       <c r="B19" t="n">
-        <v>78362</v>
+        <v>79390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2432,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471361</v>
+        <v>471491</v>
       </c>
       <c r="R19" t="n">
-        <v>6868809</v>
+        <v>6869006</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2494,54 +2503,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133794480</v>
+        <v>133791855</v>
       </c>
       <c r="B20" t="n">
-        <v>99178</v>
+        <v>78362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6487</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Laurila) Tibell</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471529</v>
+        <v>471361</v>
       </c>
       <c r="R20" t="n">
-        <v>6868615</v>
+        <v>6868809</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -2300,54 +2300,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133794480</v>
+        <v>133790857</v>
       </c>
       <c r="B18" t="n">
-        <v>99178</v>
+        <v>79390</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471529</v>
+        <v>471491</v>
       </c>
       <c r="R18" t="n">
-        <v>6868615</v>
+        <v>6869006</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2406,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133790857</v>
+        <v>133791855</v>
       </c>
       <c r="B19" t="n">
-        <v>79390</v>
+        <v>78362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,21 +2408,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2441,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471491</v>
+        <v>471361</v>
       </c>
       <c r="R19" t="n">
-        <v>6869006</v>
+        <v>6868809</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2503,45 +2494,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133791855</v>
+        <v>133794480</v>
       </c>
       <c r="B20" t="n">
-        <v>78362</v>
+        <v>99178</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471361</v>
+        <v>471529</v>
       </c>
       <c r="R20" t="n">
-        <v>6868809</v>
+        <v>6868615</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -2300,10 +2300,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133790857</v>
+        <v>133791855</v>
       </c>
       <c r="B18" t="n">
-        <v>79390</v>
+        <v>78362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,21 +2311,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2335,10 +2335,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471491</v>
+        <v>471361</v>
       </c>
       <c r="R18" t="n">
-        <v>6869006</v>
+        <v>6868809</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2397,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133791855</v>
+        <v>133790857</v>
       </c>
       <c r="B19" t="n">
-        <v>78362</v>
+        <v>79390</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,21 +2408,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2432,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471361</v>
+        <v>471491</v>
       </c>
       <c r="R19" t="n">
-        <v>6868809</v>
+        <v>6869006</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133792029</v>
       </c>
       <c r="B3" t="n">
-        <v>79437</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>133793871</v>
       </c>
       <c r="B4" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>133793537</v>
       </c>
       <c r="B5" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>133789913</v>
       </c>
       <c r="B6" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>133793581</v>
       </c>
       <c r="B7" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>133794062</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>133793754</v>
       </c>
       <c r="B10" t="n">
-        <v>80473</v>
+        <v>80474</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
         <v>133793032</v>
       </c>
       <c r="B11" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>133794314</v>
       </c>
       <c r="B12" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1800,7 +1800,7 @@
         <v>133791426</v>
       </c>
       <c r="B13" t="n">
-        <v>79390</v>
+        <v>79391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133794178</v>
       </c>
       <c r="B14" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>133791850</v>
       </c>
       <c r="B15" t="n">
-        <v>79948</v>
+        <v>79949</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>133792769</v>
       </c>
       <c r="B16" t="n">
-        <v>99178</v>
+        <v>99180</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>133791766</v>
       </c>
       <c r="B17" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2303,7 +2303,7 @@
         <v>133791855</v>
       </c>
       <c r="B18" t="n">
-        <v>78362</v>
+        <v>78363</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2397,45 +2397,54 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133790857</v>
+        <v>133794480</v>
       </c>
       <c r="B19" t="n">
-        <v>79390</v>
+        <v>99180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471491</v>
+        <v>471529</v>
       </c>
       <c r="R19" t="n">
-        <v>6869006</v>
+        <v>6868615</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2494,54 +2503,45 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133794480</v>
+        <v>133790857</v>
       </c>
       <c r="B20" t="n">
-        <v>99178</v>
+        <v>79391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471529</v>
+        <v>471491</v>
       </c>
       <c r="R20" t="n">
-        <v>6868615</v>
+        <v>6869006</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2603,7 +2603,7 @@
         <v>133794598</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79117</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -1580,7 +1580,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133793032</v>
+        <v>133794314</v>
       </c>
       <c r="B11" t="n">
         <v>99181</v>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471433</v>
+        <v>471536</v>
       </c>
       <c r="R11" t="n">
-        <v>6868656</v>
+        <v>6868645</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,11 +1660,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1691,7 +1686,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133794314</v>
+        <v>133793032</v>
       </c>
       <c r="B12" t="n">
         <v>99181</v>
@@ -1721,7 +1716,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1735,13 +1730,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471536</v>
+        <v>471433</v>
       </c>
       <c r="R12" t="n">
-        <v>6868645</v>
+        <v>6868656</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,6 +1766,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2300,45 +2300,54 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133790857</v>
+        <v>133794480</v>
       </c>
       <c r="B18" t="n">
-        <v>79391</v>
+        <v>99181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471491</v>
+        <v>471529</v>
       </c>
       <c r="R18" t="n">
-        <v>6869006</v>
+        <v>6868615</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2397,54 +2406,45 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133794480</v>
+        <v>133790857</v>
       </c>
       <c r="B19" t="n">
-        <v>99181</v>
+        <v>79391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471529</v>
+        <v>471491</v>
       </c>
       <c r="R19" t="n">
-        <v>6868615</v>
+        <v>6869006</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>133792029</v>
       </c>
       <c r="B3" t="n">
-        <v>79438</v>
+        <v>79445</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>133793871</v>
       </c>
       <c r="B4" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -978,7 +978,7 @@
         <v>133793537</v>
       </c>
       <c r="B5" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1084,7 +1084,7 @@
         <v>133789913</v>
       </c>
       <c r="B6" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1181,7 +1181,7 @@
         <v>133793581</v>
       </c>
       <c r="B7" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1389,7 +1389,7 @@
         <v>133794062</v>
       </c>
       <c r="B9" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
         <v>133793754</v>
       </c>
       <c r="B10" t="n">
-        <v>80474</v>
+        <v>80481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1580,10 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133794314</v>
+        <v>133793032</v>
       </c>
       <c r="B11" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1610,7 +1610,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1624,13 +1624,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471536</v>
+        <v>471433</v>
       </c>
       <c r="R11" t="n">
-        <v>6868645</v>
+        <v>6868656</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1660,6 +1660,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1686,10 +1691,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133793032</v>
+        <v>133794314</v>
       </c>
       <c r="B12" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1716,7 +1721,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1730,13 +1735,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471433</v>
+        <v>471536</v>
       </c>
       <c r="R12" t="n">
-        <v>6868656</v>
+        <v>6868645</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1766,11 +1771,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1800,7 +1800,7 @@
         <v>133791426</v>
       </c>
       <c r="B13" t="n">
-        <v>79391</v>
+        <v>79398</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1897,7 +1897,7 @@
         <v>133794178</v>
       </c>
       <c r="B14" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2003,7 +2003,7 @@
         <v>133791850</v>
       </c>
       <c r="B15" t="n">
-        <v>79949</v>
+        <v>79956</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2100,7 +2100,7 @@
         <v>133792769</v>
       </c>
       <c r="B16" t="n">
-        <v>99181</v>
+        <v>99188</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2206,7 +2206,7 @@
         <v>133791766</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2300,54 +2300,45 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133794480</v>
+        <v>133790857</v>
       </c>
       <c r="B18" t="n">
-        <v>99181</v>
+        <v>79398</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471529</v>
+        <v>471491</v>
       </c>
       <c r="R18" t="n">
-        <v>6868615</v>
+        <v>6869006</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2406,10 +2397,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133790857</v>
+        <v>133791855</v>
       </c>
       <c r="B19" t="n">
-        <v>79391</v>
+        <v>78370</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2417,21 +2408,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>185</v>
+        <v>6487</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2441,10 +2432,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471491</v>
+        <v>471361</v>
       </c>
       <c r="R19" t="n">
-        <v>6869006</v>
+        <v>6868809</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2503,45 +2494,54 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133791855</v>
+        <v>133794480</v>
       </c>
       <c r="B20" t="n">
-        <v>78363</v>
+        <v>99188</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6487</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471361</v>
+        <v>471529</v>
       </c>
       <c r="R20" t="n">
-        <v>6868809</v>
+        <v>6868615</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2603,7 +2603,7 @@
         <v>133794598</v>
       </c>
       <c r="B21" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -675,54 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132687492</v>
+        <v>133789913</v>
       </c>
       <c r="B2" t="n">
-        <v>99130</v>
+        <v>79405</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>185</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>471377</v>
+        <v>471488</v>
       </c>
       <c r="R2" t="n">
-        <v>6868944</v>
+        <v>6869113</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -749,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-04-22</t>
+          <t>2026-05-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>133792029</v>
+        <v>133790857</v>
       </c>
       <c r="B3" t="n">
-        <v>79445</v>
+        <v>79405</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -792,21 +783,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>864</v>
+        <v>185</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knottrig blåslav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hypogymnia bitteri</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lynge) Ahti</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -816,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>471436</v>
+        <v>471491</v>
       </c>
       <c r="R3" t="n">
-        <v>6868747</v>
+        <v>6869006</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -878,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>133793871</v>
+        <v>133791426</v>
       </c>
       <c r="B4" t="n">
-        <v>79124</v>
+        <v>79405</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -889,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>185</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Violettgrå tagellav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Bryoria nadvornikiana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -913,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>471563</v>
+        <v>471421</v>
       </c>
       <c r="R4" t="n">
-        <v>6868622</v>
+        <v>6868947</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -975,54 +966,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>133793537</v>
+        <v>133792029</v>
       </c>
       <c r="B5" t="n">
-        <v>99188</v>
+        <v>79452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>864</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Knottrig blåslav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hypogymnia bitteri</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Lynge) Ahti</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>471525</v>
+        <v>471436</v>
       </c>
       <c r="R5" t="n">
-        <v>6868589</v>
+        <v>6868747</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1081,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>133789913</v>
+        <v>133791766</v>
       </c>
       <c r="B6" t="n">
-        <v>79398</v>
+        <v>79130</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1092,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>185</v>
+        <v>6446</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1116,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>471488</v>
+        <v>471393</v>
       </c>
       <c r="R6" t="n">
-        <v>6869113</v>
+        <v>6868865</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1178,54 +1160,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>133793581</v>
+        <v>133793754</v>
       </c>
       <c r="B7" t="n">
-        <v>99188</v>
+        <v>80488</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>471520</v>
+        <v>471567</v>
       </c>
       <c r="R7" t="n">
-        <v>6868576</v>
+        <v>6868568</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1284,32 +1257,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>133790434</v>
+        <v>133791855</v>
       </c>
       <c r="B8" t="n">
-        <v>57162</v>
+        <v>78377</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>6487</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1319,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>471540</v>
+        <v>471361</v>
       </c>
       <c r="R8" t="n">
-        <v>6869075</v>
+        <v>6868809</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1355,11 +1328,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Noterat färsk spillning.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1386,32 +1354,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>133794062</v>
+        <v>133790434</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>57162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1421,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>471554</v>
+        <v>471540</v>
       </c>
       <c r="R9" t="n">
-        <v>6868632</v>
+        <v>6869075</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1457,6 +1425,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Noterat färsk spillning.</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1483,45 +1456,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>133793754</v>
+        <v>132687492</v>
       </c>
       <c r="B10" t="n">
-        <v>80481</v>
+        <v>99195</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>471567</v>
+        <v>471377</v>
       </c>
       <c r="R10" t="n">
-        <v>6868568</v>
+        <v>6868944</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1548,12 +1530,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-04-22</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1580,10 +1562,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>133793032</v>
+        <v>133792769</v>
       </c>
       <c r="B11" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1624,7 +1606,7 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>471433</v>
+        <v>471449</v>
       </c>
       <c r="R11" t="n">
         <v>6868656</v>
@@ -1660,11 +1642,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2026-05-24</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1691,10 +1668,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>133794314</v>
+        <v>133793032</v>
       </c>
       <c r="B12" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1721,7 +1698,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1735,13 +1712,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>471536</v>
+        <v>471433</v>
       </c>
       <c r="R12" t="n">
-        <v>6868645</v>
+        <v>6868656</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1771,6 +1748,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-05-24</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Fem meter söder om stormfälld tall.</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1797,45 +1779,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>133791426</v>
+        <v>133793537</v>
       </c>
       <c r="B13" t="n">
-        <v>79398</v>
+        <v>99195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>471421</v>
+        <v>471525</v>
       </c>
       <c r="R13" t="n">
-        <v>6868947</v>
+        <v>6868589</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1894,10 +1885,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>133794178</v>
+        <v>133793581</v>
       </c>
       <c r="B14" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1924,7 +1915,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1938,10 +1929,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>471548</v>
+        <v>471520</v>
       </c>
       <c r="R14" t="n">
-        <v>6868633</v>
+        <v>6868576</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2000,45 +1991,54 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>133791850</v>
+        <v>133794178</v>
       </c>
       <c r="B15" t="n">
-        <v>79956</v>
+        <v>99195</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>471361</v>
+        <v>471548</v>
       </c>
       <c r="R15" t="n">
-        <v>6868809</v>
+        <v>6868633</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2097,10 +2097,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>133792769</v>
+        <v>133794314</v>
       </c>
       <c r="B16" t="n">
-        <v>99188</v>
+        <v>99195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2127,7 +2127,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2141,13 +2141,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>471449</v>
+        <v>471536</v>
       </c>
       <c r="R16" t="n">
-        <v>6868656</v>
+        <v>6868645</v>
       </c>
       <c r="S16" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2203,45 +2203,54 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>133791766</v>
+        <v>133794480</v>
       </c>
       <c r="B17" t="n">
-        <v>79123</v>
+        <v>99195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>471393</v>
+        <v>471529</v>
       </c>
       <c r="R17" t="n">
-        <v>6868865</v>
+        <v>6868615</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2300,10 +2309,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>133790857</v>
+        <v>133793871</v>
       </c>
       <c r="B18" t="n">
-        <v>79398</v>
+        <v>79131</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2311,21 +2320,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>185</v>
+        <v>228912</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Violettgrå tagellav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria nadvornikiana</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Gyeln.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2335,10 +2344,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>471491</v>
+        <v>471563</v>
       </c>
       <c r="R18" t="n">
-        <v>6869006</v>
+        <v>6868622</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2397,10 +2406,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>133791855</v>
+        <v>133794062</v>
       </c>
       <c r="B19" t="n">
-        <v>78370</v>
+        <v>79131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2408,21 +2417,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6487</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2432,10 +2441,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>471361</v>
+        <v>471554</v>
       </c>
       <c r="R19" t="n">
-        <v>6868809</v>
+        <v>6868632</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2494,57 +2503,48 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>133794480</v>
+        <v>133794598</v>
       </c>
       <c r="B20" t="n">
-        <v>99188</v>
+        <v>79131</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Sålnbergsbodarna, Sålnbergsbodarna, Hjd</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>471529</v>
+        <v>471520</v>
       </c>
       <c r="R20" t="n">
-        <v>6868615</v>
+        <v>6868626</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2600,10 +2600,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>133794598</v>
+        <v>133791850</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79963</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2611,21 +2611,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2635,13 +2635,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>471520</v>
+        <v>471361</v>
       </c>
       <c r="R21" t="n">
-        <v>6868626</v>
+        <v>6868809</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 289-2026 artfynd.xlsx
+++ b/artfynd/A 289-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AZ21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133789913</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133790857</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133791426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133792029</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133791766</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133793754</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133791855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133790434</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132687492</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1665,6 +1715,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133792769</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1776,6 +1831,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133793032</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1882,6 +1942,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133793537</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1988,6 +2053,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133793581</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2094,6 +2164,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133794178</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2200,6 +2275,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133794314</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2306,6 +2386,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133794480</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2403,6 +2488,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133793871</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2500,6 +2590,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133794062</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2597,6 +2692,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133794598</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2694,8 +2794,35 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133791850</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>